--- a/Excel-files/purchase_activateBulk.xlsx
+++ b/Excel-files/purchase_activateBulk.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BS01503\Documents\load testing Script-BSS\Excel-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB2A405-17EE-4BFC-88B9-F6DC26CA1A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D09245F3-8AE9-4C89-B3D4-22971D05C342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Purchase (Activate)" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="51">
   <si>
     <r>
       <rPr>
@@ -28,6 +28,7 @@
         <sz val="11"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>CUSTOMER SID</t>
     </r>
@@ -37,6 +38,7 @@
         <sz val="11"/>
         <color indexed="55"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> [Required]</t>
     </r>
@@ -48,6 +50,7 @@
         <sz val="11"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>BILLING START DATE (DD-MM-YYYY)</t>
     </r>
@@ -57,6 +60,7 @@
         <sz val="11"/>
         <color indexed="55"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> [Required]</t>
     </r>
@@ -176,23 +180,44 @@
     <t>SV2600069</t>
   </si>
   <si>
-    <t>SID2609000950</t>
-  </si>
-  <si>
-    <t>SID2609000949</t>
-  </si>
-  <si>
-    <t>SID2609000947</t>
-  </si>
-  <si>
-    <t>SID2609000948</t>
+    <t>SID2609001228</t>
+  </si>
+  <si>
+    <t>SID2609001227</t>
+  </si>
+  <si>
+    <t>SID2609001226</t>
+  </si>
+  <si>
+    <t>SID2609001225</t>
+  </si>
+  <si>
+    <t>SID2609001224</t>
+  </si>
+  <si>
+    <t>SID2609001223</t>
+  </si>
+  <si>
+    <t>SID2609001222</t>
+  </si>
+  <si>
+    <t>SID2609001221</t>
+  </si>
+  <si>
+    <t>SID2609001220</t>
+  </si>
+  <si>
+    <t>SID2609001219</t>
+  </si>
+  <si>
+    <t>14-09-2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -205,30 +230,23 @@
       <sz val="11"/>
       <color indexed="9"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color indexed="55"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -240,14 +258,8 @@
         <fgColor rgb="FF467D45"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor theme="0" tint="-0.14999847407452621"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -270,36 +282,18 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -780,8 +774,8 @@
       <c r="A2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="2">
-        <v>46274</v>
+      <c r="B2" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="C2" t="s">
         <v>38</v>
@@ -797,11 +791,11 @@
       </c>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="2">
-        <v>46274</v>
+      <c r="B3" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="C3" t="s">
         <v>38</v>
@@ -817,11 +811,11 @@
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="2">
-        <v>46274</v>
+      <c r="B4" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="C4" t="s">
         <v>38</v>
@@ -837,11 +831,11 @@
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="2">
-        <v>46274</v>
+      <c r="B5" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="C5" t="s">
         <v>38</v>
@@ -853,6 +847,126 @@
         <v>39</v>
       </c>
       <c r="L5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" t="s">
+        <v>39</v>
+      </c>
+      <c r="L6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" t="s">
+        <v>39</v>
+      </c>
+      <c r="L8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9" t="s">
+        <v>39</v>
+      </c>
+      <c r="L9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J10" t="s">
+        <v>39</v>
+      </c>
+      <c r="L10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" t="s">
+        <v>37</v>
+      </c>
+      <c r="J11" t="s">
+        <v>39</v>
+      </c>
+      <c r="L11" t="s">
         <v>37</v>
       </c>
     </row>
@@ -867,6 +981,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:H5001 L2:M5001" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$AK$10001:$AK$10002</formula1>
